--- a/data/gravel/Mosaic GT-X 2025.xlsx
+++ b/data/gravel/Mosaic GT-X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757B409F-3219-C74E-B7AC-21FB02D04E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEAAB8D-3296-5B4D-A3F9-2E2366432681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2180" yWindow="500" windowWidth="26620" windowHeight="14920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -59,120 +59,51 @@
     <t>frame_size</t>
   </si>
   <si>
-    <t>frame size</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>head_tube_angle</t>
   </si>
   <si>
-    <t>HT Angle</t>
-  </si>
-  <si>
     <t>seat_tube_angle</t>
   </si>
   <si>
-    <t>ST Angle</t>
-  </si>
-  <si>
     <t>seat_tube_length</t>
   </si>
   <si>
-    <t>ST Length (C-T)</t>
-  </si>
-  <si>
     <t>top_tube_effective_length</t>
   </si>
   <si>
-    <t>TT Length (eff)</t>
-  </si>
-  <si>
     <t>head_tube_length</t>
   </si>
   <si>
-    <t>HT Length</t>
-  </si>
-  <si>
     <t>wheelbase</t>
   </si>
   <si>
-    <t>Wheelbase</t>
-  </si>
-  <si>
     <t>chainstay_length</t>
   </si>
   <si>
-    <t>Chainstay Length</t>
-  </si>
-  <si>
     <t>fork_offset_rake</t>
   </si>
   <si>
-    <t>Fork Offset</t>
-  </si>
-  <si>
     <t>trail</t>
   </si>
   <si>
-    <t>Trail</t>
-  </si>
-  <si>
     <t>standover</t>
   </si>
   <si>
-    <t>Standover</t>
-  </si>
-  <si>
     <t>bottom_bracket_drop</t>
   </si>
   <si>
-    <t>BB Drop</t>
-  </si>
-  <si>
     <t>bottom_bracket_height</t>
   </si>
   <si>
-    <t>BB Height</t>
-  </si>
-  <si>
     <t>top_tube_angle</t>
   </si>
   <si>
-    <t>TT Angle</t>
-  </si>
-  <si>
     <t>stack</t>
   </si>
   <si>
-    <t>Frame Stack</t>
-  </si>
-  <si>
     <t>reach</t>
   </si>
   <si>
-    <t>Frame Reach</t>
-  </si>
-  <si>
     <t>crank_length</t>
   </si>
   <si>
@@ -368,10 +299,109 @@
     <t>rider_max</t>
   </si>
   <si>
-    <t>a8:i33</t>
-  </si>
-  <si>
     <t>https://mosaiccycles.com/our-bikes/gravel/</t>
+  </si>
+  <si>
+    <t>Measurement (units)</t>
+  </si>
+  <si>
+    <t>S (50)</t>
+  </si>
+  <si>
+    <t>S/M (52)</t>
+  </si>
+  <si>
+    <t>M (54)</t>
+  </si>
+  <si>
+    <t>M/L (55)</t>
+  </si>
+  <si>
+    <t>L (56)</t>
+  </si>
+  <si>
+    <t>XL (58)</t>
+  </si>
+  <si>
+    <t>XXL (60)</t>
+  </si>
+  <si>
+    <t>HT Angle (deg)</t>
+  </si>
+  <si>
+    <t>ST Angle (deg)</t>
+  </si>
+  <si>
+    <t>ST Length (C-T, mm)</t>
+  </si>
+  <si>
+    <t>TT Length (effective, mm)</t>
+  </si>
+  <si>
+    <t>HT Length (mm)</t>
+  </si>
+  <si>
+    <t>Wheelbase (mm)</t>
+  </si>
+  <si>
+    <t>Chainstay Length (mm)</t>
+  </si>
+  <si>
+    <t>Fork Offset (mm)</t>
+  </si>
+  <si>
+    <t>Trail (mm)</t>
+  </si>
+  <si>
+    <t>Standover (mm)</t>
+  </si>
+  <si>
+    <t>BB Drop (mm)</t>
+  </si>
+  <si>
+    <t>BB Height (mm)</t>
+  </si>
+  <si>
+    <t>TT Angle (deg)</t>
+  </si>
+  <si>
+    <t>Frame Stack (mm)</t>
+  </si>
+  <si>
+    <t>Frame Reach (mm)</t>
+  </si>
+  <si>
+    <t>TT Diameter (mm)</t>
+  </si>
+  <si>
+    <t>ST Diameter (mm)</t>
+  </si>
+  <si>
+    <t>DT Diameter (mm)</t>
+  </si>
+  <si>
+    <t>SS Diameter (mm)</t>
+  </si>
+  <si>
+    <t>CS Diameter (mm)</t>
+  </si>
+  <si>
+    <t>tt_diameter</t>
+  </si>
+  <si>
+    <t>st_diameter</t>
+  </si>
+  <si>
+    <t>dt_diameter</t>
+  </si>
+  <si>
+    <t>ss_diameter</t>
+  </si>
+  <si>
+    <t>cs_diameter</t>
+  </si>
+  <si>
+    <t>a8:i38</t>
   </si>
 </sst>
 </file>
@@ -711,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -730,7 +760,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -754,12 +784,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -767,7 +797,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -775,36 +805,36 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>69</v>
@@ -830,10 +860,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C10">
         <v>74.5</v>
@@ -859,39 +889,39 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E11">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F11">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="G11">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="H11">
         <v>580</v>
       </c>
       <c r="I11">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>530</v>
@@ -917,10 +947,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>115</v>
@@ -946,10 +976,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>1054</v>
@@ -975,10 +1005,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C15">
         <v>445</v>
@@ -1004,10 +1034,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="C16">
         <v>56</v>
@@ -1033,10 +1063,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C17">
         <v>82</v>
@@ -1062,10 +1092,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>791</v>
@@ -1091,10 +1121,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C19">
         <v>75</v>
@@ -1120,10 +1150,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="C20">
         <v>293</v>
@@ -1149,10 +1179,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="C21">
         <v>7.5</v>
@@ -1178,10 +1208,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="C22">
         <v>551</v>
@@ -1207,10 +1237,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C23">
         <v>373</v>
@@ -1236,414 +1266,538 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
+      </c>
+      <c r="B24" t="s">
+        <v>112</v>
       </c>
       <c r="C24">
+        <v>34.9</v>
+      </c>
+      <c r="D24">
+        <v>34.9</v>
+      </c>
+      <c r="E24">
+        <v>34.9</v>
+      </c>
+      <c r="F24">
+        <v>34.9</v>
+      </c>
+      <c r="G24">
+        <v>34.9</v>
+      </c>
+      <c r="H24">
+        <v>34.9</v>
+      </c>
+      <c r="I24">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25">
+        <v>31.8</v>
+      </c>
+      <c r="D25">
+        <v>31.8</v>
+      </c>
+      <c r="E25">
+        <v>31.8</v>
+      </c>
+      <c r="F25">
+        <v>31.8</v>
+      </c>
+      <c r="G25">
+        <v>31.8</v>
+      </c>
+      <c r="H25">
+        <v>31.8</v>
+      </c>
+      <c r="I25">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26">
+        <v>38.1</v>
+      </c>
+      <c r="D26">
+        <v>38.1</v>
+      </c>
+      <c r="E26">
+        <v>38.1</v>
+      </c>
+      <c r="F26">
+        <v>38.1</v>
+      </c>
+      <c r="G26">
+        <v>38.1</v>
+      </c>
+      <c r="H26">
+        <v>38.1</v>
+      </c>
+      <c r="I26">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>16</v>
+      </c>
+      <c r="F27">
+        <v>16</v>
+      </c>
+      <c r="G27">
+        <v>16</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
+      </c>
+      <c r="I27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29">
         <v>406</v>
       </c>
-      <c r="D24">
+      <c r="D29">
         <v>406</v>
       </c>
-      <c r="E24">
+      <c r="E29">
         <v>406</v>
       </c>
-      <c r="F24">
+      <c r="F29">
         <v>406</v>
       </c>
-      <c r="G24">
+      <c r="G29">
         <v>406</v>
       </c>
-      <c r="H24">
+      <c r="H29">
         <v>406</v>
       </c>
-      <c r="I24">
+      <c r="I29">
         <v>406</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29">
-        <v>29</v>
-      </c>
-      <c r="D29">
-        <v>29</v>
-      </c>
-      <c r="E29">
-        <v>29</v>
-      </c>
-      <c r="F29">
-        <v>29</v>
-      </c>
-      <c r="G29">
-        <v>29</v>
-      </c>
-      <c r="H29">
-        <v>29</v>
-      </c>
-      <c r="I29">
-        <v>29</v>
+      <c r="J29" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30">
-        <v>55</v>
-      </c>
-      <c r="D30">
-        <v>55</v>
-      </c>
-      <c r="E30">
-        <v>55</v>
-      </c>
-      <c r="F30">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>55</v>
-      </c>
-      <c r="H30">
-        <v>55</v>
-      </c>
-      <c r="I30">
-        <v>55</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>29</v>
+      </c>
+      <c r="E34">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>29</v>
+      </c>
+      <c r="G34">
+        <v>29</v>
+      </c>
+      <c r="H34">
+        <v>29</v>
+      </c>
+      <c r="I34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35">
         <v>55</v>
       </c>
-      <c r="D31">
+      <c r="D35">
         <v>55</v>
       </c>
-      <c r="E31">
+      <c r="E35">
         <v>55</v>
       </c>
-      <c r="F31">
+      <c r="F35">
         <v>55</v>
       </c>
-      <c r="G31">
+      <c r="G35">
         <v>55</v>
       </c>
-      <c r="H31">
+      <c r="H35">
         <v>55</v>
       </c>
-      <c r="I31">
+      <c r="I35">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36">
         <v>55</v>
       </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>55</v>
+      </c>
+      <c r="E36">
+        <v>55</v>
+      </c>
+      <c r="F36">
+        <v>55</v>
+      </c>
+      <c r="G36">
+        <v>55</v>
+      </c>
+      <c r="H36">
+        <v>55</v>
+      </c>
+      <c r="I36">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48">
-        <v>142</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49">
-        <v>100</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>42</v>
+      </c>
+      <c r="B53">
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B54">
-        <v>42</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>100</v>
+        <v>48</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
+      </c>
+      <c r="C59" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>53</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>84</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>61</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B74" t="s">
-        <v>105</v>
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mosaic GT-X 2025.xlsx
+++ b/data/gravel/Mosaic GT-X 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEAAB8D-3296-5B4D-A3F9-2E2366432681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467FEDEB-6395-524C-AD47-47850A6DA225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2180" yWindow="500" windowWidth="26620" windowHeight="14920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -402,6 +402,24 @@
   </si>
   <si>
     <t>a8:i38</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -741,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1609,27 +1627,27 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -1637,7 +1655,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -1645,158 +1663,188 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>44</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>46</v>
       </c>
-      <c r="B57">
+      <c r="B63">
         <v>27.2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>48</v>
       </c>
-      <c r="B59">
+      <c r="B65">
         <v>42</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C65" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>61</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>63</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>67</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B85" t="s">
         <v>82</v>
       </c>
     </row>
